--- a/Testes/reescala/Teste populacao e gerações/Teste10/3_melhor_escala.xlsx
+++ b/Testes/reescala/Teste populacao e gerações/Teste10/3_melhor_escala.xlsx
@@ -1117,11 +1117,11 @@
       <c r="AE5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="5" t="n">
-        <v>0</v>
+      <c r="AF5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AH5" s="5" t="n">
         <v>0</v>
@@ -1294,8 +1294,8 @@
       <c r="P7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" s="4" t="n">
-        <v>1</v>
+      <c r="Q7" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R7" s="4" t="n">
         <v>1</v>
@@ -2404,8 +2404,8 @@
       <c r="P17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="4" t="n">
-        <v>1</v>
+      <c r="Q17" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>1</v>
@@ -3442,11 +3442,11 @@
       <c r="AC26" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD26" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE26" s="5" t="n">
-        <v>0</v>
+      <c r="AD26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AF26" s="5" t="n">
         <v>0</v>
@@ -3565,11 +3565,11 @@
       <c r="AG27" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AH27" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI27" s="5" t="n">
-        <v>0</v>
+      <c r="AH27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3865,11 +3865,11 @@
       <c r="V30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="W30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="4" t="n">
-        <v>1</v>
+      <c r="W30" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Y30" s="5" t="n">
         <v>0</v>
@@ -3979,11 +3979,11 @@
       <c r="W31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="X31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="4" t="n">
-        <v>1</v>
+      <c r="X31" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="Z31" s="5" t="n">
         <v>0</v>
@@ -4180,8 +4180,8 @@
       <c r="P33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q33" s="4" t="n">
-        <v>1</v>
+      <c r="Q33" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R33" s="4" t="n">
         <v>1</v>
@@ -4513,8 +4513,8 @@
       <c r="P36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q36" s="5" t="n">
-        <v>0</v>
+      <c r="Q36" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R36" s="4" t="n">
         <v>1</v>
@@ -4561,14 +4561,14 @@
       <c r="AF36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" s="4" t="n">
-        <v>1</v>
+      <c r="AG36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI36" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -4624,8 +4624,8 @@
       <c r="P37" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q37" s="5" t="n">
-        <v>0</v>
+      <c r="Q37" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R37" s="4" t="n">
         <v>1</v>
@@ -4957,8 +4957,8 @@
       <c r="P40" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" s="5" t="n">
-        <v>0</v>
+      <c r="Q40" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R40" s="4" t="n">
         <v>1</v>
@@ -5290,8 +5290,8 @@
       <c r="P43" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" s="5" t="n">
-        <v>0</v>
+      <c r="Q43" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R43" s="5" t="n">
         <v>0</v>
@@ -5401,8 +5401,8 @@
       <c r="P44" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q44" s="4" t="n">
-        <v>1</v>
+      <c r="Q44" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R44" s="4" t="n">
         <v>1</v>
@@ -5512,8 +5512,8 @@
       <c r="P45" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="Q45" s="5" t="n">
-        <v>0</v>
+      <c r="Q45" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="R45" s="4" t="n">
         <v>1</v>
@@ -5884,20 +5884,20 @@
       <c r="AC48" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH48" s="5" t="n">
-        <v>0</v>
+      <c r="AD48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="AI48" s="5" t="n">
         <v>0</v>
@@ -5956,8 +5956,8 @@
       <c r="P49" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" s="4" t="n">
-        <v>1</v>
+      <c r="Q49" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="R49" s="4" t="n">
         <v>1</v>
@@ -6226,11 +6226,11 @@
       <c r="AF51" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AG51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="4" t="n">
-        <v>1</v>
+      <c r="AG51" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH51" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="AI51" s="5" t="n">
         <v>0</v>
